--- a/LB_Program_Statements.xlsx
+++ b/LB_Program_Statements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\LB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C810E-2D1A-43C8-9819-90AA829DD214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C9AD68-EB41-401C-B1F3-AC2656FF2048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{529304FC-C76E-4A78-91F7-2381E30A6342}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="868">
   <si>
     <t>Jay Ganesh print in c</t>
   </si>
@@ -3065,6 +3065,464 @@
   </si>
   <si>
     <t>DataBase.remove(1);</t>
+  </si>
+  <si>
+    <t>automorphic number
+number square 
+square last digitd equal to number
+best apporach</t>
+  </si>
+  <si>
+    <t>Database.clear();
+       Database = null;
+       System.gc();</t>
+  </si>
+  <si>
+    <t>CSV convert
+ FileWriter fwobj = new FileWriter(Filename);
+       fwobj.write("Data,Subject,Duration.Description\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV convert try catch </t>
+  </si>
+  <si>
+    <t>StudyTracker class which has all functions
+user -&gt; main(shell) -&gt; StudyTracker -&gt; StudyLog -&gt; DB(CSV)</t>
+  </si>
+  <si>
+    <t>StudyTracker class which has all functions
+user -&gt; main(shell) -&gt; StudyTracker -&gt; StudyLog -&gt; DB(CSV)
+class StudyTracker
+{
+    public ArrayList &lt;StudyLog&gt;Database = new ArrayList&lt;StudyLog&gt;(); no constructor</t>
+  </si>
+  <si>
+    <t>//Shell to interact with end user</t>
+  </si>
+  <si>
+    <t>StudyTracker class empty class template</t>
+  </si>
+  <si>
+    <t>StudyTracker InsertLog function ISSUE in description input takin</t>
+  </si>
+  <si>
+    <t>ISSUE RESOLVED sobj.nextLine();</t>
+  </si>
+  <si>
+    <t>Display log function</t>
+  </si>
+  <si>
+    <t>Export to csv function</t>
+  </si>
+  <si>
+    <t>HashMap
+HashMap &lt;Integer, String&gt;hobj = new HashMap&lt;Integer, String&gt;();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TreeMap
+TreeMap &lt;Integer, String&gt;hobj = new TreeMap&lt;Integer, String&gt;();
+treemap keys are sorted not in hashmap </t>
+  </si>
+  <si>
+    <t>TreeMap
+key duplicate not allowed get overwrited</t>
+  </si>
+  <si>
+    <t>System.out.println(hobj.firstKey());
+        System.out.println(hobj.lastKey()); System.out.println(hobj.firstEntry());
+        System.out.println(hobj.lastEntry());</t>
+  </si>
+  <si>
+    <t>System.out.println(hobj.higherKey(20));
+        System.out.println(hobj.lowerKey(20));</t>
+  </si>
+  <si>
+    <t>load from csv to code try opp</t>
+  </si>
+  <si>
+    <t>Summary by date function i project</t>
+  </si>
+  <si>
+    <t>Summary by subject sampla</t>
+  </si>
+  <si>
+    <t>ArrayX class for 
+Accept and display methods</t>
+  </si>
+  <si>
+    <t>ArrayX implements GetterSetter</t>
+  </si>
+  <si>
+    <t>class Searching extends ArrayX</t>
+  </si>
+  <si>
+    <t>class ArrayX implements GetterSetter
+{
+    protected int Arr[];
+    protected int iSize;</t>
+  </si>
+  <si>
+    <t>final class Searching extends ArrayX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINEAR search </t>
+  </si>
+  <si>
+    <t>Bidirectionla methos search</t>
+  </si>
+  <si>
+    <t>CheckSorted Array function</t>
+  </si>
+  <si>
+    <t>BinarySearch</t>
+  </si>
+  <si>
+    <t>ajava</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> if(CheckSorted() == false)
+        {
+            return BiDirectionalSearch(iNo);
+        }</t>
+  </si>
+  <si>
+    <t>BinarySearch
+ if(Arr[iMid] == iNo || Arr[iStart] == iNo || Arr[iEnd] == iNo)
+            {
+                bFlag = true;
+                break;
+            }</t>
+  </si>
+  <si>
+    <t>if(CheckSorted() == false)
+        {
+            return false;
+        }</t>
+  </si>
+  <si>
+    <t>if(iNo &lt; Arr[iStart] || iNo &gt; Arr[iEnd])
+        {
+            return false;
+        }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> while taking input from user
+ if(i &gt; 0 &amp;&amp; (Arr[i-1] &gt; Arr[i]))
+            {
+                isSorted = false;
+            }</t>
+  </si>
+  <si>
+    <t>dynamic user input</t>
+  </si>
+  <si>
+    <t>Sorting class extends ArrayX class</t>
+  </si>
+  <si>
+    <t>Arrays class operations
+Arrays.sort(Arr);</t>
+  </si>
+  <si>
+    <t>Arrays class operations
+Arrays.sort(Arr);
+end toindex is not inclusive fromindex is inclusive</t>
+  </si>
+  <si>
+    <t>JVA</t>
+  </si>
+  <si>
+    <t>Arrays.sort(Arr, Collections.reverseOrder());   for descending order
+Integer class use as datatype in array</t>
+  </si>
+  <si>
+    <t>int index = Arrays.binarySearch(Arr, 21);</t>
+  </si>
+  <si>
+    <t>Sorting class extends ArrayX class
+Bubble sort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete Searching Code </t>
+  </si>
+  <si>
+    <t>Sorting class  only</t>
+  </si>
+  <si>
+    <t>Selection sort</t>
+  </si>
+  <si>
+    <t>Selection sort with pass</t>
+  </si>
+  <si>
+    <t>Insertion sort</t>
+  </si>
+  <si>
+    <t>Singly linear link list class creation</t>
+  </si>
+  <si>
+    <t>Singly linear link list
+InsertFirst</t>
+  </si>
+  <si>
+    <t>Singly linear link list</t>
+  </si>
+  <si>
+    <t>Singly linear link list Display and count</t>
+  </si>
+  <si>
+    <t>InsertLast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rabbit tottoise for finding middle element </t>
+  </si>
+  <si>
+    <t>fast -&gt; +2 slow +1</t>
+  </si>
+  <si>
+    <t>loop creation in LL
+infinite Display loop</t>
+  </si>
+  <si>
+    <t>CheckLoop function using rabbit tortise 
+lop present</t>
+  </si>
+  <si>
+    <t>CheckLoop function using rabbit tortise 
+not loop present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MiddleElement using for loop using iCount/2 </t>
+  </si>
+  <si>
+    <t>if(iCnt &gt; iCount)
+            {
+                bFlag = true;
+                break;
+            }</t>
+  </si>
+  <si>
+    <t>Reverse the linkedlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">io madhale sagale checked exception detat so catch it </t>
+  </si>
+  <si>
+    <t>FTP server project for Arithematic derver started
+server created as listening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server for mathematical operations </t>
+  </si>
+  <si>
+    <t>Client for mathematical operations</t>
+  </si>
+  <si>
+    <t>Clirnt for ftp for commands handling template</t>
+  </si>
+  <si>
+    <t>if(parts.length != 2)
+                    {
+                        System.out.println("Usage : PUT &lt;FileName&gt;");
+                        continue;
+                    }</t>
+  </si>
+  <si>
+    <t>SERVER for FTP handling command</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTP server get put </t>
+  </si>
+  <si>
+    <t>FTP client</t>
+  </si>
+  <si>
+    <t>FTP server</t>
+  </si>
+  <si>
+    <t>collection framework in java
+employee attendence analyzer using hashmap</t>
+  </si>
+  <si>
+    <t>employee attendence analyzer
+for(Map.Entry&lt;Integer, Integer&gt;eobj : frequency.entrySet())</t>
+  </si>
+  <si>
+    <t>employee attendence analyzer
+for(int id : frequency.keySet())</t>
+  </si>
+  <si>
+    <t>JAAV</t>
+  </si>
+  <si>
+    <t>employee attendence analyzer
+ frequency.put(id, frequency.getOrDefault(id,0)+1);</t>
+  </si>
+  <si>
+    <t>leetcode like template</t>
+  </si>
+  <si>
+    <t>Command line input
+String A is empty</t>
+  </si>
+  <si>
+    <t>Command line arguments 
+int main(int argc, char *argv[]) by default exe name considered</t>
+  </si>
+  <si>
+    <t>loop to iterate A string command line</t>
+  </si>
+  <si>
+    <t>./Myexe 10 11
+Addition  error as argv is char array so int not done</t>
+  </si>
+  <si>
+    <t>./Myexe 10 11
+Addition  error as argv is chr warning</t>
+  </si>
+  <si>
+    <t>./Myexe 10 11
+Addition ans = atoi(argv[1]) + atoi(argv[2]);
+atoi included in stdlib</t>
+  </si>
+  <si>
+    <t>java program949.java 10 11
+command line argument addition strings get concatinated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ans = Integer.parseInt(A[0]) + Integer.parseInt(A[1]) ;  </t>
+  </si>
+  <si>
+    <t>first non repeating char in string
+java program951.java programming    to run this
+tREEMAP stores alphabatically Issue in ordering</t>
+  </si>
+  <si>
+    <t>LinkedHashMap 
+stores key as we insert and main insertion order</t>
+  </si>
+  <si>
+    <t>LinkedHashMap 
+stores key as we insert and main insertion order
+first non repetating char</t>
+  </si>
+  <si>
+    <t>LinkedHashMap 
+ for(Map.Entry&lt;Character,Integer&gt; eobj : frequency.entrySet())
+first non repetating char</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e commerce website stock in out </t>
+  </si>
+  <si>
+    <t>duplicate transaction identifier
+using hashset with 2 hashset</t>
+  </si>
+  <si>
+    <t>if(unique.add(str))
+            {
+            }
+            else
+            {
+                duplicate.add(str);
+            }</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bRet = unique.add(str);
+            if(bRet == false)
+            {
+                duplicate.add(str);
+            }</t>
+  </si>
+  <si>
+    <t>Collections.sort(aobj);</t>
+  </si>
+  <si>
+    <t>System.out.println("Amit".compareTo("Amit"));</t>
+  </si>
+  <si>
+    <t>Design patterns starting (Singlrton)
+class Demo with constructor</t>
+  </si>
+  <si>
+    <t>Design patterns starting (Singlrton)
+class Demo with private constructor so compilesd time error</t>
+  </si>
+  <si>
+    <t>Demo obj2; private constructor 
+reference created</t>
+  </si>
+  <si>
+    <t>ParkingLot class with private constructor
+private static ParkingLot instance;</t>
+  </si>
+  <si>
+    <t>Factory Design pattern 
+Enum code</t>
+  </si>
+  <si>
+    <t>abstract vvehicle is extedded by car, bike and truck</t>
+  </si>
+  <si>
+    <t>Factory design pattern
+VehivleFactory class
+// Default missing error in switch case</t>
+  </si>
+  <si>
+    <t>Factory design pattern
+VehivleFactory class
+// Default solved by returning null</t>
+  </si>
+  <si>
+    <t>Factory design pattern
+default:
+                throw new IllegalArgumentException("Invalid vehicle type");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System.out.println(pobj1 == pobj2); true Singleton final </t>
+  </si>
+  <si>
+    <t>Builder design pattern which handle creation of 
+object of class having multiple arguments</t>
+  </si>
+  <si>
+    <t>Singleton</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>private members</t>
+  </si>
+  <si>
+    <t>Display function in class ticket</t>
+  </si>
+  <si>
+    <t>Builder class with set methods</t>
+  </si>
+  <si>
+    <t>ParkingTicket pobj = new Builder()
+        .setTicketNumber(11)
+        .setVehicleNumber("MH12VL 9080")
+        .setFloorNumber(4)
+        .setSpotNumber(89)
+        .setEntryTime("10.30 AM")
+        .build();</t>
+  </si>
+  <si>
+    <t>canonical function calling</t>
+  </si>
+  <si>
+    <t>Builder design</t>
+  </si>
+  <si>
+    <t>canonical function calling
+ananomus object no name</t>
+  </si>
+  <si>
+    <t>Observer design pattern</t>
+  </si>
+  <si>
+    <t>JAVAs</t>
   </si>
 </sst>
 </file>
@@ -3515,7 +3973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A099BD82-CF9E-4D41-BD71-1A037607BD64}">
-  <dimension ref="A1:C849"/>
+  <dimension ref="A1:C994"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="106.140625" bestFit="1" customWidth="1"/>
@@ -9069,6 +9527,30 @@
         <v>731</v>
       </c>
     </row>
+    <row r="827" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A827" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B827" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A828" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B828" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A829" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B829" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="830" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
         <v>732</v>
@@ -9209,6 +9691,905 @@
       </c>
       <c r="B849" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A850" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B850" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A851" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B851" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A852" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B852" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A853" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B853" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A854" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B854" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A855" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B855" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A856" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B856" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A857" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B857" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A858" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B858" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A859" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A860" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B860" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A861" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B861" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A862" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B862" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A863" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B863" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A864" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B864" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A865" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B865" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A866" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B866" t="s">
+        <v>102</v>
+      </c>
+      <c r="C866" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A867" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B867" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A868" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B868" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A869" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B869" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A870" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B870" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A871" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B871" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A872" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B872" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A873" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B873" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A874" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A875" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B875" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A876" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B876" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A877" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B877" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A878" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B878" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A879" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B879" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A880" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B880" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A881" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B881" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A882" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B882" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A883" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B883" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A884" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B884" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A885" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B885" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A886" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B886" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A887" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B887" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A888" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B888" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A889" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B889" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A895" t="s">
+        <v>794</v>
+      </c>
+      <c r="B895" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A896" t="s">
+        <v>795</v>
+      </c>
+      <c r="B896" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A897" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="B897" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A898" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A899" t="s">
+        <v>798</v>
+      </c>
+      <c r="B899" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A900" t="s">
+        <v>799</v>
+      </c>
+      <c r="B900" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A901" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B901" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A902" t="s">
+        <v>801</v>
+      </c>
+      <c r="B902" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A903" t="s">
+        <v>802</v>
+      </c>
+      <c r="B903" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A904" t="s">
+        <v>803</v>
+      </c>
+      <c r="B904" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>809</v>
+      </c>
+      <c r="B909" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>804</v>
+      </c>
+      <c r="B910" t="s">
+        <v>102</v>
+      </c>
+      <c r="C910" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A912" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B912" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A913" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B913" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A914" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B914" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A915" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B915" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A916" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B916" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A917" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B917" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A918" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B918" t="s">
+        <v>102</v>
+      </c>
+      <c r="C918" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>814</v>
+      </c>
+      <c r="B924" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>815</v>
+      </c>
+      <c r="B925" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>816</v>
+      </c>
+      <c r="B926" t="s">
+        <v>102</v>
+      </c>
+      <c r="C926" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>818</v>
+      </c>
+      <c r="B927" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>819</v>
+      </c>
+      <c r="B932" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>821</v>
+      </c>
+      <c r="B934" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>820</v>
+      </c>
+      <c r="B935" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A936" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B936" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A937" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B937" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A938" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B938" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A939" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B939" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A940" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B940" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A942" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B942" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A943" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B943" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A944" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="B944" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A946" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B946" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A947" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B947" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A948" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B948" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A949" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B949" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A950" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B950" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A951" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B951" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A952" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="B952" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A953" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="B953" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A954" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B954" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A955" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B955" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A956" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B956" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A957" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B957" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A959" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B959" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+      <c r="A960" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B960" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="A961" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B961" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>844</v>
+      </c>
+      <c r="B965" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>845</v>
+      </c>
+      <c r="B967" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A970" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B970" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A971" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B971" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A972" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="B972" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A973" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B973" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A974" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B974" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A975" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B975" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A977" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B977" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A978" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B978" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A979" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B979" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A980" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B980" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A981" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B981" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A982" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B982" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A983" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B983" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A984" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B984" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A985" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B985" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A986" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B986" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A987" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B987" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A990" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B990" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A991" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B991" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A993" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B993" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A994" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="B994" t="s">
+        <v>867</v>
       </c>
     </row>
   </sheetData>

--- a/LB_Program_Statements.xlsx
+++ b/LB_Program_Statements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\LB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C9AD68-EB41-401C-B1F3-AC2656FF2048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA8B4F5-12F1-4F30-803C-B3D287941A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{529304FC-C76E-4A78-91F7-2381E30A6342}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="877">
   <si>
     <t>Jay Ganesh print in c</t>
   </si>
@@ -3523,6 +3523,33 @@
   </si>
   <si>
     <t>JAVAs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JavaScript variables </t>
+  </si>
+  <si>
+    <t>JS</t>
+  </si>
+  <si>
+    <t>let for block only scope, var for all program scope const for non modifiable</t>
+  </si>
+  <si>
+    <t>function declaration using function keyword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addition function </t>
+  </si>
+  <si>
+    <t>function Addition(Value1, Value2) generic without datatype</t>
+  </si>
+  <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>odd even number</t>
+  </si>
+  <si>
+    <t>for loop</t>
   </si>
 </sst>
 </file>
@@ -3973,7 +4000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A099BD82-CF9E-4D41-BD71-1A037607BD64}">
-  <dimension ref="A1:C994"/>
+  <dimension ref="A1:C1033"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="106.140625" bestFit="1" customWidth="1"/>
@@ -10592,6 +10619,57 @@
         <v>867</v>
       </c>
     </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>868</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>869</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>871</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>872</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>873</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>875</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1033" t="s">
+        <v>876</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>869</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LB_Program_Statements.xlsx
+++ b/LB_Program_Statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\LB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA8B4F5-12F1-4F30-803C-B3D287941A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114B9998-3E40-4402-9013-4DFFA78BAE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{529304FC-C76E-4A78-91F7-2381E30A6342}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="886">
   <si>
     <t>Jay Ganesh print in c</t>
   </si>
@@ -3550,6 +3550,33 @@
   </si>
   <si>
     <t>for loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfect number function usung for loop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">addtion of factors is equal to number itself </t>
+  </si>
+  <si>
+    <t>while loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">digits summation function </t>
+  </si>
+  <si>
+    <t>Array let Arr = [ 12,23]</t>
+  </si>
+  <si>
+    <t>jS</t>
+  </si>
+  <si>
+    <t>typeof inbuild function</t>
+  </si>
+  <si>
+    <t>String traversal</t>
+  </si>
+  <si>
+    <t>count small characters are</t>
   </si>
 </sst>
 </file>
@@ -4000,7 +4027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A099BD82-CF9E-4D41-BD71-1A037607BD64}">
-  <dimension ref="A1:C1033"/>
+  <dimension ref="A1:C1046"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="106.140625" bestFit="1" customWidth="1"/>
@@ -10638,7 +10665,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="1028" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>872</v>
       </c>
@@ -10646,7 +10673,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="1029" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>873</v>
       </c>
@@ -10654,7 +10681,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="1030" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>875</v>
       </c>
@@ -10662,12 +10689,71 @@
         <v>874</v>
       </c>
     </row>
-    <row r="1033" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>876</v>
       </c>
       <c r="B1033" t="s">
         <v>869</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1035" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>874</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1036" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1037" t="s">
+        <v>880</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1039" t="s">
+        <v>881</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>883</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>884</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>
